--- a/data/trans_camb/IQ2608_R3-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IQ2608_R3-Clase-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>26,31</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>22,92</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8,65</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>25,04</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>27,75</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>12,88</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>26,31</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>22,92</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,44</t>
+          <t>12,08</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>11,44</t>
+          <t>10,63</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,59; 36,45</t>
+          <t>15,93; 36,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,02; 39,77</t>
+          <t>13,19; 32,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 27,93</t>
+          <t>-8,61; 23,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,77; 35,78</t>
+          <t>13,88; 34,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,36; 33,03</t>
+          <t>16,56; 37,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 23,97</t>
+          <t>-4,5; 28,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,02; 32,92</t>
+          <t>18,22; 32,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18,06; 33,08</t>
+          <t>17,99; 32,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 22,54</t>
+          <t>-2,75; 21,27</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>43,36%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>37,78%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>14,26%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>46,34%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>51,35%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>23,83%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>43,36%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>37,78%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>18,57%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>25,57; 79,24</t>
+          <t>23,6; 67,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>28,89; 84,66</t>
+          <t>19,89; 63,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 59,06</t>
+          <t>-13,21; 42,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24,25; 66,67</t>
+          <t>23,1; 71,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,45; 62,66</t>
+          <t>27,64; 78,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-10,65; 43,76</t>
+          <t>-7,2; 57,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,07; 62,93</t>
+          <t>28,96; 62,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>29,65; 63,73</t>
+          <t>29,42; 63,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 41,42</t>
+          <t>-4,51; 38,63</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>18,28</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>17,15</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-7,75</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>25,84</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>23,24</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>7,8</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>18,28</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>17,15</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-8,86</t>
+          <t>7,26</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,25</t>
+          <t>0,15</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,24; 35,48</t>
+          <t>8,48; 27,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,99; 33,49</t>
+          <t>8,05; 27,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,4; 22,34</t>
+          <t>-29,58; 9,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,72; 27,05</t>
+          <t>15,36; 35,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,39; 25,97</t>
+          <t>12,24; 33,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-28,97; 11,57</t>
+          <t>-11,48; 22,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,41; 29,62</t>
+          <t>14,61; 28,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,86; 26,93</t>
+          <t>13,74; 27,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-14,44; 11,84</t>
+          <t>-13,95; 12,11</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>26,37%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>24,75%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-11,18%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>41,68%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>37,48%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>12,58%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>26,37%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>24,75%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-12,78%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-0,37%</t>
+          <t>0,22%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>23,69; 65,47</t>
+          <t>11,35; 45,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,78; 63,01</t>
+          <t>10,5; 45,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-16,4; 38,57</t>
+          <t>-41,01; 15,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,77; 44,29</t>
+          <t>22,57; 65,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,8; 41,36</t>
+          <t>17,58; 62,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-40,32; 16,63</t>
+          <t>-16,01; 39,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,71; 49,07</t>
+          <t>20,89; 46,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,32; 44,46</t>
+          <t>19,59; 44,73</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-21,03; 19,07</t>
+          <t>-20,28; 19,64</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>25,54</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>17,73</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>14,29</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>19,12</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>8,36</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-10,87</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>25,54</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>17,73</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,57</t>
+          <t>-11,89</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5,08</t>
+          <t>3,34</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,11; 29,95</t>
+          <t>13,71; 35,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 20,86</t>
+          <t>6,14; 28,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-39,36; 16,45</t>
+          <t>-8,95; 32,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,89; 36,59</t>
+          <t>7,72; 30,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,24; 28,62</t>
+          <t>-4,75; 21,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 32,52</t>
+          <t>-37,43; 14,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,73; 30,04</t>
+          <t>14,67; 29,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,28; 22,92</t>
+          <t>5,12; 21,46</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-13,52; 19,39</t>
+          <t>-14,38; 19,14</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>43,1%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>29,92%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>24,12%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>29,87%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>13,07%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-16,99%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>43,1%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>29,92%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>-18,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,98; 53,69</t>
+          <t>20,89; 66,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 36,19</t>
+          <t>9,62; 55,13</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-57,37; 26,86</t>
+          <t>-14,01; 58,62</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22,97; 69,96</t>
+          <t>10,74; 54,37</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,6; 54,29</t>
+          <t>-6,72; 38,63</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-11,15; 60,62</t>
+          <t>-56,94; 23,01</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23,84; 54,16</t>
+          <t>21,86; 52,27</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,94; 40,6</t>
+          <t>7,93; 38,61</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-21,02; 33,87</t>
+          <t>-21,92; 32,59</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>15,91</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>20,23</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>11,59</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>14,49</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>14,92</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>7,39</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>15,91</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>20,23</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,11</t>
+          <t>6,73</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>9,44</t>
+          <t>9,35</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,42; 21,77</t>
+          <t>9,16; 23,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,17; 21,68</t>
+          <t>13,31; 27,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 19,45</t>
+          <t>-2,42; 23,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8,79; 23,0</t>
+          <t>6,9; 21,39</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>13,17; 26,29</t>
+          <t>8,09; 21,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 23,03</t>
+          <t>-7,67; 19,06</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,39; 20,01</t>
+          <t>10,35; 20,73</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12,37; 22,08</t>
+          <t>12,39; 22,23</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 18,03</t>
+          <t>-0,46; 17,82</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>23,89%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>30,37%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>17,41%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>21,79%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>22,43%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>11,11%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>23,89%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>30,37%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,05%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10,34; 35,3</t>
+          <t>12,8; 37,34</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11,36; 35,14</t>
+          <t>19,25; 43,84</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-9,11; 30,03</t>
+          <t>-3,62; 37,57</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12,39; 37,09</t>
+          <t>9,79; 34,21</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>18,69; 42,67</t>
+          <t>11,15; 33,39</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 35,7</t>
+          <t>-11,07; 29,74</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,74; 31,22</t>
+          <t>15,02; 33,13</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>17,9; 34,94</t>
+          <t>17,63; 35,33</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 27,55</t>
+          <t>-0,63; 27,73</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>12,26</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>24,42</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>9,71</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>16,97</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>24,78</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>5,12</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>12,26</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>24,42</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,85</t>
+          <t>0,12</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>9,07</t>
+          <t>6,81</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,84; 26,76</t>
+          <t>3,24; 21,51</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>14,9; 34,5</t>
+          <t>15,1; 33,07</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-14,12; 23,36</t>
+          <t>-5,48; 23,39</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,73; 21,69</t>
+          <t>7,47; 27,33</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>15,79; 32,86</t>
+          <t>15,19; 33,44</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 23,12</t>
+          <t>-19,11; 18,31</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,73; 21,28</t>
+          <t>8,32; 21,49</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>18,31; 31,18</t>
+          <t>18,11; 31,32</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 19,5</t>
+          <t>-4,67; 18,05</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>20,16%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>40,13%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>15,95%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>29,23%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>42,7%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>8,81%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>20,16%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>40,13%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>11,43%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>10,68; 51,82</t>
+          <t>4,9; 39,12</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>22,98; 67,77</t>
+          <t>23,53; 61,89</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-23,54; 43,07</t>
+          <t>-9,3; 40,85</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4,21; 39,2</t>
+          <t>11,81; 52,7</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>23,72; 61,06</t>
+          <t>23,51; 65,86</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 40,91</t>
+          <t>-30,99; 33,36</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,11; 38,53</t>
+          <t>13,3; 39,41</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>28,36; 56,47</t>
+          <t>28,48; 57,62</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 34,72</t>
+          <t>-7,4; 31,8</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>18,13</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>8,11</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-12,67</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>36,86</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>18,92</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-2,74</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>18,13</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>8,11</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-8,4</t>
+          <t>-1,72</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-4,25</t>
+          <t>-6,73</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>23,54; 47,82</t>
+          <t>5,5; 29,14</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>5,74; 32,78</t>
+          <t>-5,87; 20,38</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-28,97; 21,03</t>
+          <t>-33,07; 6,64</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6,45; 29,33</t>
+          <t>24,7; 48,34</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 19,87</t>
+          <t>6,06; 32,08</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-28,54; 12,6</t>
+          <t>-27,55; 24,22</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,71; 35,1</t>
+          <t>19,22; 36,06</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>4,75; 22,79</t>
+          <t>5,34; 23,75</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-19,71; 11,72</t>
+          <t>-22,98; 9,49</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>28,28%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>12,65%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>-19,76%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>72,64%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>37,28%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-5,41%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>28,28%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>12,65%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-13,11%</t>
+          <t>-3,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-7,42%</t>
+          <t>-11,76%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>40,84; 114,61</t>
+          <t>8,33; 52,43</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>11,64; 78,72</t>
+          <t>-7,33; 35,5</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-53,26; 45,44</t>
+          <t>-50,19; 10,72</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>9,09; 52,86</t>
+          <t>43,01; 116,16</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 34,16</t>
+          <t>11,01; 72,41</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-41,78; 19,28</t>
+          <t>-49,14; 50,68</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>28,69; 69,34</t>
+          <t>30,66; 70,51</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>8,06; 44,01</t>
+          <t>8,37; 44,69</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-33,14; 21,69</t>
+          <t>-38,72; 15,95</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>18,41</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>19,86</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>5,43</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>20,82</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>20,07</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>5,45</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>18,41</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>19,86</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,2</t>
+          <t>4,14</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>6,06</t>
+          <t>5,01</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>16,63; 24,96</t>
+          <t>14,67; 22,14</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>15,64; 23,6</t>
+          <t>16,14; 23,61</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 12,43</t>
+          <t>-2,03; 12,02</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14,19; 22,17</t>
+          <t>16,77; 24,75</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>15,99; 23,6</t>
+          <t>15,81; 24,39</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 12,48</t>
+          <t>-2,74; 11,39</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,81; 22,32</t>
+          <t>16,8; 22,16</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>17,21; 22,7</t>
+          <t>17,29; 22,63</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,83; 11,11</t>
+          <t>0,15; 9,97</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>28,9%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>31,17%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>8,53%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>34,49%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>33,25%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>9,02%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>28,9%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>31,17%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>8,07%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>26,25; 43,29</t>
+          <t>22,31; 36,35</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>24,94; 40,74</t>
+          <t>24,49; 38,41</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 21,08</t>
+          <t>-3,19; 19,16</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>21,56; 36,28</t>
+          <t>26,78; 43,05</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>23,73; 38,5</t>
+          <t>24,98; 42,06</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 20,25</t>
+          <t>-4,39; 19,38</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,4; 36,9</t>
+          <t>26,3; 37,04</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>27,01; 37,59</t>
+          <t>27,12; 37,61</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1,41; 18,22</t>
+          <t>0,2; 16,36</t>
         </is>
       </c>
     </row>
